--- a/Fase 2/Evidencias Proyecto/Evidencias de sistema/Base de datos/contactos.xlsx
+++ b/Fase 2/Evidencias Proyecto/Evidencias de sistema/Base de datos/contactos.xlsx
@@ -469,7 +469,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>9900000051</t>
+          <t>5092891721</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -494,7 +494,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>+56999000001</t>
+          <t>+56980002754</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -514,7 +514,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>9900000084</t>
+          <t>8593997503</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -539,7 +539,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>+56999000002</t>
+          <t>+56996874484</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -559,7 +559,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>9900000084</t>
+          <t>8593997503</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -584,7 +584,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>+56999000003</t>
+          <t>+56926393507</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -604,7 +604,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>9900000032</t>
+          <t>3738975628</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -629,7 +629,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>+56999000004</t>
+          <t>+56993914244</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>9900000032</t>
+          <t>3738975628</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -694,7 +694,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>9900000017</t>
+          <t>2327139357</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -739,7 +739,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>9900000017</t>
+          <t>2327139357</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>+56999000005</t>
+          <t>+56988939057</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>9900000017</t>
+          <t>2327139357</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -809,7 +809,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>+56999000006</t>
+          <t>+56956368156</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -829,7 +829,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>9900000091</t>
+          <t>9054925374</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>+56999000007</t>
+          <t>+56964304013</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>9900000091</t>
+          <t>9054925374</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>+56999000008</t>
+          <t>+56975863067</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -919,7 +919,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>9900000041</t>
+          <t>4458192345</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -944,7 +944,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>+56999000009</t>
+          <t>+56958575520</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>9900000041</t>
+          <t>4458192345</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1009,7 +1009,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>9900000035</t>
+          <t>3879702798</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1034,7 +1034,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>+56999000010</t>
+          <t>+56946248600</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1054,7 +1054,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>9900000035</t>
+          <t>3879702798</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1079,7 +1079,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>+56999000011</t>
+          <t>+56959279643</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>9900000080</t>
+          <t>8304482332</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1144,7 +1144,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>9900000080</t>
+          <t>8304482332</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1169,7 +1169,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>+56999000012</t>
+          <t>+56936098572</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1189,7 +1189,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>9900000079</t>
+          <t>8294244131</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1214,7 +1214,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>+56999000013</t>
+          <t>+56924597160</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1234,7 +1234,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>9900000079</t>
+          <t>8294244131</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>+56999000014</t>
+          <t>+56981374654</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1279,7 +1279,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>9900000079</t>
+          <t>8294244131</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1304,7 +1304,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>+56999000015</t>
+          <t>+56986155157</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>9900000001</t>
+          <t>1142203221</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1369,7 +1369,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>9900000001</t>
+          <t>1142203221</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1414,7 +1414,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>9900000071</t>
+          <t>7380470856</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>+56999000016</t>
+          <t>+56981447513</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>9900000088</t>
+          <t>8865815672</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1484,7 +1484,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>+56999000017</t>
+          <t>+56933002231</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>9900000088</t>
+          <t>8865815672</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1529,7 +1529,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>+56999000018</t>
+          <t>+56944354402</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1549,7 +1549,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>9900000062</t>
+          <t>6406638629</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1574,7 +1574,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>+56999000019</t>
+          <t>+56994297440</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1594,7 +1594,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>9900000062</t>
+          <t>6406638629</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>+56999000020</t>
+          <t>+56915302065</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1639,7 +1639,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>9900000072</t>
+          <t>7435668134</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>+56999000021</t>
+          <t>+56916903388</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>9900000072</t>
+          <t>7435668134</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>la contraparte comercial</t>
+          <t>Javiera</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1709,7 +1709,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>+56999000022</t>
+          <t>+56958922860</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>9900000072</t>
+          <t>7435668134</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1754,7 +1754,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>+56999000023</t>
+          <t>+56945561174</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1774,7 +1774,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>9900000047</t>
+          <t>4936254645</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1819,7 +1819,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>9900000012</t>
+          <t>1853803852</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1844,7 +1844,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>+56999000024</t>
+          <t>+56911363139</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1864,7 +1864,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>9900000012</t>
+          <t>1853803852</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1889,7 +1889,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>+56999000025</t>
+          <t>+56990241687</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1909,7 +1909,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>9900000012</t>
+          <t>1853803852</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1934,7 +1934,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>+56999000026</t>
+          <t>+56965985879</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -1954,7 +1954,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>9900000022</t>
+          <t>2534379800</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1979,7 +1979,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>+56999000027</t>
+          <t>+56962170162</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -1999,7 +1999,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>9900000049</t>
+          <t>5026590100</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2044,7 +2044,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>9900000049</t>
+          <t>5026590100</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2069,7 +2069,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>+56999000028</t>
+          <t>+56943406752</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2089,7 +2089,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>9900000073</t>
+          <t>7462729157</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>+56999000029</t>
+          <t>+56954591543</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2134,7 +2134,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>9900000073</t>
+          <t>7462729157</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>+56999000030</t>
+          <t>+56986333653</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2179,7 +2179,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>9900000070</t>
+          <t>7064661963</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2204,7 +2204,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>+56999000031</t>
+          <t>+56978374563</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2224,7 +2224,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>9900000070</t>
+          <t>7064661963</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2249,7 +2249,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>+56999000032</t>
+          <t>+56921741106</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2269,7 +2269,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>9900000003</t>
+          <t>1315393763</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2294,7 +2294,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>+56999000033</t>
+          <t>+56976875826</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2314,7 +2314,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>9900000003</t>
+          <t>1315393763</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2339,7 +2339,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>+56999000034</t>
+          <t>+56945759511</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -2359,7 +2359,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>9900000010</t>
+          <t>1733295235</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>+56999000035</t>
+          <t>+56932227407</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>9900000010</t>
+          <t>1733295235</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
